--- a/training_records_export.xlsx
+++ b/training_records_export.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="4.90909090909091" customWidth="1" min="4" max="4"/>
@@ -1094,30 +1094,40 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>培训日期</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>考试成绩</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>有效期限</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>区域权限</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>人员在各单位间流动情况</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>最近一次培训日期</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>特殊工种证有效期</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1126,45 +1136,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>大麻子</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>汉族</t>
+          <t>汉</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>610103196512051360</t>
+          <t>11010119900307881X</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18709256788</t>
+          <t>13899999999</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>四川华庭生活区</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>四川华庭</t>
+          <t>测试建筑工程有限公司</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>钢筋工</t>
+          <t>普工</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1172,21 +1182,25 @@
           <t>大专</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>三元肥</t>
-        </is>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>95</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>大虎</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1196,35 +1210,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>汉族</t>
+          <t>汉</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>610103197805123696</t>
+          <t>11010119900307882Y</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13259960968</t>
+          <t>13899999998</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>四川华庭生活区</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>四川华庭</t>
+          <t>测试建筑工程有限公司</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>泥工</t>
+          <t>焊工</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1233,15 +1247,278 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>三元肥</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>大麻子</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>汉族</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>61</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>610103196512051360</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>18709256788</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>四川华庭生活区</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>钢筋工</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>大专</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>大虎</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>汉族</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>48</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>610103197805123696</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>13259960968</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>四川华庭生活区</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>泥工</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>大专</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>孙斌</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>汉族</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>38</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>610103198802201630</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>13310947563</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>四川华庭生活区</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>安全员</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>大专</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>孙斌</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>xx</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-5864</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>123456789012345678</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>13310947563</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>安全员</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>大专</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>李小丽</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>汉族</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>36</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>110101199003072345</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>13800138000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>北京市朝阳区幸福路100号</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>电气焊工</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>大专</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
